--- a/data/trans_orig/IP31KM05_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM05_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31989</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28594</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40767</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36522</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43645</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32856</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41167</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>78450</t>
+          <t>69791</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72275</t>
+          <t>65077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83228</t>
+          <t>73172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5446</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3137</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8841</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5728</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9973</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>15039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>133210</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125034</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>139692</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>130168</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>120646</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>137258</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>75,74%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>86,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>154039</t>
+          <t>118984</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144855</t>
+          <t>110652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161411</t>
+          <t>125260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>284208</t>
+          <t>252193</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>270601</t>
+          <t>241150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295371</t>
+          <t>261645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23832</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17350</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32008</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29131</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22041</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38653</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20548</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>34866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>50367</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45888</t>
+          <t>40915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70658</t>
+          <t>61410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>164843</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>154212</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>174267</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>139809</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>128556</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>148386</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>74,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>172484</t>
+          <t>142761</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159105</t>
+          <t>132585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183005</t>
+          <t>150070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>312295</t>
+          <t>307604</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296209</t>
+          <t>293878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>326656</t>
+          <t>319793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35283</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25859</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45914</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>33263</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24686</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>44516</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>31911</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>24602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53385</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>73268</t>
+          <t>67194</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>55005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89354</t>
+          <t>80920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>235969</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>222487</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>250010</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>80,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>76,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>215532</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>201147</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>234867</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>78,58%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>73,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>244553</t>
+          <t>195807</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227010</t>
+          <t>183118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>257600</t>
+          <t>207048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>460085</t>
+          <t>431777</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>436379</t>
+          <t>410538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>480240</t>
+          <t>448524</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56252</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42211</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>69734</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>58735</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39400</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>73120</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60446</t>
+          <t>59530</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47399</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77989</t>
+          <t>72219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>119181</t>
+          <t>115781</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99026</t>
+          <t>99034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142887</t>
+          <t>137020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>566010</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>547310</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>583530</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>79,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>734</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>526278</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>506008</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>547004</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>80,58%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>77,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>495355</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>584740</t>
+          <t>478057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>626642</t>
+          <t>510739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1135038</t>
+          <t>1061364</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1105313</t>
+          <t>1036479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1163495</t>
+          <t>1086227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120814</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>103294</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139514</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>126856</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106130</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>147126</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>135973</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>107469</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159993</t>
+          <t>140151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,22 +2280,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>262829</t>
+          <t>243667</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234372</t>
+          <t>218804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292554</t>
+          <t>268552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
